--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893831</v>
+        <v>129893853</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>92194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550516</v>
+        <v>550467</v>
       </c>
       <c r="R6" t="n">
-        <v>7121651</v>
+        <v>7121578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893853</v>
+        <v>129893852</v>
       </c>
       <c r="B7" t="n">
-        <v>92194</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550467</v>
+        <v>550639</v>
       </c>
       <c r="R7" t="n">
-        <v>7121578</v>
+        <v>7121729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893852</v>
+        <v>129893831</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550639</v>
+        <v>550516</v>
       </c>
       <c r="R8" t="n">
-        <v>7121729</v>
+        <v>7121651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129893838</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129893830</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129893822</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129893823</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893853</v>
+        <v>129893852</v>
       </c>
       <c r="B6" t="n">
-        <v>92194</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550467</v>
+        <v>550639</v>
       </c>
       <c r="R6" t="n">
-        <v>7121578</v>
+        <v>7121729</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893852</v>
+        <v>129893831</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550639</v>
+        <v>550516</v>
       </c>
       <c r="R7" t="n">
-        <v>7121729</v>
+        <v>7121651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893831</v>
+        <v>129893853</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>92197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550516</v>
+        <v>550467</v>
       </c>
       <c r="R8" t="n">
-        <v>7121651</v>
+        <v>7121578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893834</v>
+        <v>129893837</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550661</v>
+        <v>550510</v>
       </c>
       <c r="R9" t="n">
-        <v>7121714</v>
+        <v>7121582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1445,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129893837</v>
+        <v>129893834</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550510</v>
+        <v>550661</v>
       </c>
       <c r="R10" t="n">
-        <v>7121582</v>
+        <v>7121714</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,7 +1576,7 @@
         <v>129893847</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129893835</v>
       </c>
       <c r="B12" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>129893821</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893833</v>
+        <v>129893829</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550652</v>
+        <v>550344</v>
       </c>
       <c r="R14" t="n">
-        <v>7121708</v>
+        <v>7121439</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,6 +1945,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893829</v>
+        <v>129893833</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>80189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550344</v>
+        <v>550652</v>
       </c>
       <c r="R15" t="n">
-        <v>7121439</v>
+        <v>7121708</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,11 +2047,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2076,7 +2076,7 @@
         <v>129893845</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129893849</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>129893832</v>
       </c>
       <c r="B18" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893819</v>
+        <v>129893850</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550656</v>
+        <v>550629</v>
       </c>
       <c r="R19" t="n">
-        <v>7121708</v>
+        <v>7121759</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,6 +2445,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2471,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893850</v>
+        <v>129893819</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>91602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2482,21 +2487,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2506,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550629</v>
+        <v>550656</v>
       </c>
       <c r="R20" t="n">
-        <v>7121759</v>
+        <v>7121708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2542,11 +2547,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2576,7 +2576,7 @@
         <v>129893820</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129893848</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893852</v>
+        <v>129893831</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550639</v>
+        <v>550516</v>
       </c>
       <c r="R6" t="n">
-        <v>7121729</v>
+        <v>7121651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893831</v>
+        <v>129893852</v>
       </c>
       <c r="B7" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550516</v>
+        <v>550639</v>
       </c>
       <c r="R7" t="n">
-        <v>7121651</v>
+        <v>7121729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893837</v>
+        <v>129893834</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550510</v>
+        <v>550661</v>
       </c>
       <c r="R9" t="n">
-        <v>7121582</v>
+        <v>7121714</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129893834</v>
+        <v>129893837</v>
       </c>
       <c r="B10" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550661</v>
+        <v>550510</v>
       </c>
       <c r="R10" t="n">
-        <v>7121714</v>
+        <v>7121582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1542,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893829</v>
+        <v>129893833</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550344</v>
+        <v>550652</v>
       </c>
       <c r="R14" t="n">
-        <v>7121439</v>
+        <v>7121708</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,11 +1945,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893833</v>
+        <v>129893829</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550652</v>
+        <v>550344</v>
       </c>
       <c r="R15" t="n">
-        <v>7121708</v>
+        <v>7121439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,6 +2042,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2374,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893850</v>
+        <v>129893819</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>91602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550629</v>
+        <v>550656</v>
       </c>
       <c r="R19" t="n">
-        <v>7121759</v>
+        <v>7121708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,11 +2445,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,10 +2471,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893819</v>
+        <v>129893850</v>
       </c>
       <c r="B20" t="n">
-        <v>91602</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,21 +2482,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,10 +2506,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550656</v>
+        <v>550629</v>
       </c>
       <c r="R20" t="n">
-        <v>7121708</v>
+        <v>7121759</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,6 +2542,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893831</v>
+        <v>129893853</v>
       </c>
       <c r="B6" t="n">
-        <v>80189</v>
+        <v>92197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550516</v>
+        <v>550467</v>
       </c>
       <c r="R6" t="n">
-        <v>7121651</v>
+        <v>7121578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893853</v>
+        <v>129893831</v>
       </c>
       <c r="B8" t="n">
-        <v>92197</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550467</v>
+        <v>550516</v>
       </c>
       <c r="R8" t="n">
-        <v>7121578</v>
+        <v>7121651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893819</v>
+        <v>129893850</v>
       </c>
       <c r="B19" t="n">
-        <v>91602</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550656</v>
+        <v>550629</v>
       </c>
       <c r="R19" t="n">
-        <v>7121708</v>
+        <v>7121759</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,6 +2445,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2471,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893850</v>
+        <v>129893819</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>91602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2482,21 +2487,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2506,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550629</v>
+        <v>550656</v>
       </c>
       <c r="R20" t="n">
-        <v>7121759</v>
+        <v>7121708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2542,11 +2547,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129893838</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129893830</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129893822</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129893823</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129893853</v>
       </c>
       <c r="B6" t="n">
-        <v>92197</v>
+        <v>92200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893852</v>
+        <v>129893831</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550639</v>
+        <v>550516</v>
       </c>
       <c r="R7" t="n">
-        <v>7121729</v>
+        <v>7121651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893831</v>
+        <v>129893852</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550516</v>
+        <v>550639</v>
       </c>
       <c r="R8" t="n">
-        <v>7121651</v>
+        <v>7121729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893834</v>
+        <v>129893837</v>
       </c>
       <c r="B9" t="n">
-        <v>80189</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550661</v>
+        <v>550510</v>
       </c>
       <c r="R9" t="n">
-        <v>7121714</v>
+        <v>7121582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1445,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129893837</v>
+        <v>129893834</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>80192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550510</v>
+        <v>550661</v>
       </c>
       <c r="R10" t="n">
-        <v>7121582</v>
+        <v>7121714</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,7 +1576,7 @@
         <v>129893847</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129893835</v>
       </c>
       <c r="B12" t="n">
-        <v>91616</v>
+        <v>91619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>129893821</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>129893833</v>
       </c>
       <c r="B14" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129893829</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>129893845</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129893849</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>129893832</v>
       </c>
       <c r="B18" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893850</v>
+        <v>129893819</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>91605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550629</v>
+        <v>550656</v>
       </c>
       <c r="R19" t="n">
-        <v>7121759</v>
+        <v>7121708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,11 +2445,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,10 +2471,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893819</v>
+        <v>129893850</v>
       </c>
       <c r="B20" t="n">
-        <v>91602</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,21 +2482,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,10 +2506,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550656</v>
+        <v>550629</v>
       </c>
       <c r="R20" t="n">
-        <v>7121708</v>
+        <v>7121759</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,6 +2542,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2576,7 +2576,7 @@
         <v>129893820</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129893848</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893833</v>
+        <v>129893829</v>
       </c>
       <c r="B14" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550652</v>
+        <v>550344</v>
       </c>
       <c r="R14" t="n">
-        <v>7121708</v>
+        <v>7121439</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,6 +1945,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893829</v>
+        <v>129893833</v>
       </c>
       <c r="B15" t="n">
-        <v>57740</v>
+        <v>80192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550344</v>
+        <v>550652</v>
       </c>
       <c r="R15" t="n">
-        <v>7121439</v>
+        <v>7121708</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,11 +2047,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129893838</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129893830</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893853</v>
+        <v>129893831</v>
       </c>
       <c r="B6" t="n">
-        <v>92200</v>
+        <v>80193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550467</v>
+        <v>550516</v>
       </c>
       <c r="R6" t="n">
-        <v>7121578</v>
+        <v>7121651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893831</v>
+        <v>129893852</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550516</v>
+        <v>550639</v>
       </c>
       <c r="R7" t="n">
-        <v>7121651</v>
+        <v>7121729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893852</v>
+        <v>129893853</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>92201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550639</v>
+        <v>550467</v>
       </c>
       <c r="R8" t="n">
-        <v>7121729</v>
+        <v>7121578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,7 +1377,7 @@
         <v>129893837</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129893834</v>
       </c>
       <c r="B10" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>129893847</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129893835</v>
       </c>
       <c r="B12" t="n">
-        <v>91619</v>
+        <v>91620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893829</v>
+        <v>129893833</v>
       </c>
       <c r="B14" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550344</v>
+        <v>550652</v>
       </c>
       <c r="R14" t="n">
-        <v>7121439</v>
+        <v>7121708</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,11 +1945,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893833</v>
+        <v>129893829</v>
       </c>
       <c r="B15" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550652</v>
+        <v>550344</v>
       </c>
       <c r="R15" t="n">
-        <v>7121708</v>
+        <v>7121439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,6 +2042,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2076,7 +2076,7 @@
         <v>129893845</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129893849</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>129893832</v>
       </c>
       <c r="B18" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893819</v>
+        <v>129893850</v>
       </c>
       <c r="B19" t="n">
-        <v>91605</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550656</v>
+        <v>550629</v>
       </c>
       <c r="R19" t="n">
-        <v>7121708</v>
+        <v>7121759</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,6 +2445,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2471,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893850</v>
+        <v>129893819</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>91606</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2482,21 +2487,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2506,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550629</v>
+        <v>550656</v>
       </c>
       <c r="R20" t="n">
-        <v>7121759</v>
+        <v>7121708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2542,11 +2547,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,7 +2678,7 @@
         <v>129893848</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129893838</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129893830</v>
       </c>
       <c r="B3" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893831</v>
+        <v>129893853</v>
       </c>
       <c r="B6" t="n">
-        <v>80193</v>
+        <v>92218</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550516</v>
+        <v>550467</v>
       </c>
       <c r="R6" t="n">
-        <v>7121651</v>
+        <v>7121578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893852</v>
+        <v>129893831</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>80194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550639</v>
+        <v>550516</v>
       </c>
       <c r="R7" t="n">
-        <v>7121729</v>
+        <v>7121651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893853</v>
+        <v>129893852</v>
       </c>
       <c r="B8" t="n">
-        <v>92201</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550467</v>
+        <v>550639</v>
       </c>
       <c r="R8" t="n">
-        <v>7121578</v>
+        <v>7121729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893837</v>
+        <v>129893834</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>80194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550510</v>
+        <v>550661</v>
       </c>
       <c r="R9" t="n">
-        <v>7121582</v>
+        <v>7121714</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129893834</v>
+        <v>129893837</v>
       </c>
       <c r="B10" t="n">
-        <v>80193</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550661</v>
+        <v>550510</v>
       </c>
       <c r="R10" t="n">
-        <v>7121714</v>
+        <v>7121582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1542,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,7 +1576,7 @@
         <v>129893847</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129893835</v>
       </c>
       <c r="B12" t="n">
-        <v>91620</v>
+        <v>91637</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>129893833</v>
       </c>
       <c r="B14" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>129893845</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129893849</v>
       </c>
       <c r="B17" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>129893832</v>
       </c>
       <c r="B18" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893850</v>
+        <v>129893819</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>91623</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550629</v>
+        <v>550656</v>
       </c>
       <c r="R19" t="n">
-        <v>7121759</v>
+        <v>7121708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,11 +2445,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,10 +2471,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893819</v>
+        <v>129893850</v>
       </c>
       <c r="B20" t="n">
-        <v>91606</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,21 +2482,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,10 +2506,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550656</v>
+        <v>550629</v>
       </c>
       <c r="R20" t="n">
-        <v>7121708</v>
+        <v>7121759</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,6 +2542,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,7 +2678,7 @@
         <v>129893848</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893852</v>
+        <v>129893831</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550639</v>
+        <v>550516</v>
       </c>
       <c r="R6" t="n">
-        <v>7121729</v>
+        <v>7121651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893831</v>
+        <v>129893852</v>
       </c>
       <c r="B8" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550516</v>
+        <v>550639</v>
       </c>
       <c r="R8" t="n">
-        <v>7121651</v>
+        <v>7121729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893829</v>
+        <v>129893833</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550344</v>
+        <v>550652</v>
       </c>
       <c r="R14" t="n">
-        <v>7121439</v>
+        <v>7121708</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,11 +1945,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893833</v>
+        <v>129893829</v>
       </c>
       <c r="B15" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550652</v>
+        <v>550344</v>
       </c>
       <c r="R15" t="n">
-        <v>7121708</v>
+        <v>7121439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,6 +2042,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893831</v>
+        <v>129893853</v>
       </c>
       <c r="B6" t="n">
-        <v>80200</v>
+        <v>92236</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550516</v>
+        <v>550467</v>
       </c>
       <c r="R6" t="n">
-        <v>7121651</v>
+        <v>7121578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893853</v>
+        <v>129893852</v>
       </c>
       <c r="B7" t="n">
-        <v>92234</v>
+        <v>79095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550467</v>
+        <v>550639</v>
       </c>
       <c r="R7" t="n">
-        <v>7121578</v>
+        <v>7121729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893852</v>
+        <v>129893831</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550639</v>
+        <v>550516</v>
       </c>
       <c r="R8" t="n">
-        <v>7121729</v>
+        <v>7121651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1678,7 +1678,7 @@
         <v>129893835</v>
       </c>
       <c r="B12" t="n">
-        <v>91653</v>
+        <v>91655</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893850</v>
+        <v>129893819</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>91641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550629</v>
+        <v>550656</v>
       </c>
       <c r="R19" t="n">
-        <v>7121759</v>
+        <v>7121708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,11 +2445,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,10 +2471,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893819</v>
+        <v>129893850</v>
       </c>
       <c r="B20" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,21 +2482,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,10 +2506,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550656</v>
+        <v>550629</v>
       </c>
       <c r="R20" t="n">
-        <v>7121708</v>
+        <v>7121759</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,6 +2542,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6576-2025 artfynd.xlsx
+++ b/artfynd/A 6576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129893838</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129893830</v>
       </c>
       <c r="B3" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129893822</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129893823</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893853</v>
+        <v>129893831</v>
       </c>
       <c r="B6" t="n">
-        <v>92236</v>
+        <v>80285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550467</v>
+        <v>550516</v>
       </c>
       <c r="R6" t="n">
-        <v>7121578</v>
+        <v>7121651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
         <v>129893852</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893831</v>
+        <v>129893853</v>
       </c>
       <c r="B8" t="n">
-        <v>80200</v>
+        <v>92323</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550516</v>
+        <v>550467</v>
       </c>
       <c r="R8" t="n">
-        <v>7121651</v>
+        <v>7121578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
         <v>129893837</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129893834</v>
       </c>
       <c r="B10" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>129893847</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129893835</v>
       </c>
       <c r="B12" t="n">
-        <v>91655</v>
+        <v>91742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>129893821</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893833</v>
+        <v>129893829</v>
       </c>
       <c r="B14" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550652</v>
+        <v>550344</v>
       </c>
       <c r="R14" t="n">
-        <v>7121708</v>
+        <v>7121439</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,6 +1945,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893829</v>
+        <v>129893833</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550344</v>
+        <v>550652</v>
       </c>
       <c r="R15" t="n">
-        <v>7121439</v>
+        <v>7121708</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,11 +2047,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2076,7 +2076,7 @@
         <v>129893845</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129893849</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>129893832</v>
       </c>
       <c r="B18" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>129893819</v>
       </c>
       <c r="B19" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>129893850</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>129893820</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129893848</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
